--- a/results/job_matches_2026-08-29.xlsx
+++ b/results/job_matches_2026-08-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc487e12b46c0c21</t>
+          <t>https://www.indeed.com/viewjob?jk=2d9b5bcc98f7ba12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, clustering keys, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc487e12b46c0c21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>COREHIRE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6002f30e875ad9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=aef7e5280c3704dc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Stf - E4</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Bragg, NC, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, clustering keys, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862b277963d1774e</t>
+          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chervon North America</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Scala, Oracle, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea2b6207934b593</t>
+          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
+          <t>Machine Learning &amp; Data Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cb1d159dbef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=efe070deedac1b9a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Data Operations Engineer</t>
+          <t>Data Engineering Summer/Fall Co-Op (June - Dec '27)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
+          <t>https://www.indeed.com/viewjob?jk=8446a0ee2fc12124</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>BI / Data Architect (Remote)-3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe070deedac1b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineering Summer/Fall Co-Op (June - Dec '27)</t>
+          <t>Associate, Software Engineer - SMA Solutions</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,124 +951,124 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8446a0ee2fc12124</t>
+          <t>https://www.indeed.com/viewjob?jk=1d538b0abcf938eb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)-3</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ziff Davis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Database Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inadev Corporation</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44742e2d35b42b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a530d898f0f57a3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer - SMA Solutions</t>
+          <t>Jr DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Koniag Government Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d538b0abcf938eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f140f3b3c4a71d9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Salesforce Subject Matter Expert (SME) - DoD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ziff Davis</t>
+          <t>Vissat Solutions, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
+          <t>https://www.indeed.com/viewjob?jk=20324e69621e6432</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Cloud Architect – Contract Opportunity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>IT LINK, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Downey, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a530d898f0f57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=847eafed624da6b1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Salesforce Subject Matter Expert (SME) - DoD</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vissat Solutions, Inc</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20324e69621e6432</t>
+          <t>https://www.indeed.com/viewjob?jk=68b9213bf9a10955</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect – Contract Opportunity</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IT LINK, LLC</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Downey, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847eafed624da6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7eb57f3ad62c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Front End/Back End (Library of Congress)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87eb22f496fe7839</t>
+          <t>https://www.indeed.com/viewjob?jk=cd63cf544b64f9bc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd63cf544b64f9bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1a302f6fb7238092</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,129 +1301,129 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a302f6fb7238092</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oliver Wyman Vector - DevOps Engineer (AWS &amp; Cybersecurity)</t>
+          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5025df0e29ed9ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Senior Data Engineer-3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
+          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer (B2B)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429cbc163ce4bf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-3</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Data &amp; Database Engineer – Modernization &amp; AI Infrastructure</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8231054ab092224b</t>
+          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (B2B)</t>
+          <t>Senior Analytics Engineer, Finance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlboro, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
+          <t>https://www.indeed.com/viewjob?jk=38276618e771db29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior CE Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
+          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
+          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Finance</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Valley Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marlboro, MA, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38276618e771db29</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior CE Data Engineer</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Software Engineer - Vehicle Experience Services</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
+          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Valley Health</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect – Contract Position</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007f823364fb3e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
+          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Experience Services</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
+          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
+          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
+          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
+          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
+          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
+          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
+          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
+          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
+          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
+          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
+          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
+          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
+          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
+          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
+          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
+          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
+          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
+          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
+          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
+          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
+          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
+          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
+          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
+          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
+          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>ProMach</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Engineer, AI Support</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Insurance Institute for Business and Home Safety</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Richburg, SC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Azure, Spark, Scala, NoSQL, Data Modeling, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data, Analytics &amp; Cloud Engineering Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Kenway Consulting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
+          <t>https://www.indeed.com/viewjob?jk=1164a9e1e0387fdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Bedminster, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Support</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Insurance Institute for Business and Home Safety</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Richburg, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, NoSQL, Data Modeling, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
+          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data, Analytics &amp; Cloud Engineering Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kenway Consulting</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1164a9e1e0387fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HealthTronics</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5df17bcfce4703</t>
+          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineering Consultant</t>
+          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bedminster, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Clearlink</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Clearlink</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
+          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Security Assurance Engineer</t>
+          <t>New College Grad - Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a2c9a53e534603</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfb93ed65fbd759</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,94 +3961,94 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>New College Grad - Software Engineer</t>
+          <t>Sr. Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Focus on the Family</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, ETL, Power BI, Tableau</t>
+          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfb93ed65fbd759</t>
+          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Data Engineer Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data Up Consulting</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43c47f699ab58bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer Analyst</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Data Up Consulting</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Spark, PySpark, PostgreSQL, ELT, Power BI, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce1cb75163081c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer Snowflake/Agentic AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, PostgreSQL, ELT, Power BI, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce1cb75163081c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ebf36281f9e5d65</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer Snowflake/Agentic AI</t>
+          <t>Python Developer Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Valtech Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebf36281f9e5d65</t>
+          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Python Developer Engineer II</t>
+          <t>Python Developer Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Python Developer Engineer</t>
+          <t>Azure Solutions Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf200ceba06f2e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Associate Software Engineer--SAP</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Credit One Bank</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Tableau, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b3516dfc64a416</t>
+          <t>https://www.indeed.com/viewjob?jk=0bad4738b1c25e8b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Azure Solutions Architect</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf200ceba06f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=54be710cc09718e6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Department Of Public Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, SQL Server, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
+          <t>https://www.indeed.com/viewjob?jk=576601d5caea8556</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Department Of Public Health</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, SQL Server, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,444 +4346,444 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576601d5caea8556</t>
+          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer--SAP</t>
+          <t>Senior Full-Stack Software Engineer (Python / React)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Docker, Kubernetes, AKS, pytest, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bad4738b1c25e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, Docker, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54be710cc09718e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1efae92e327259</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Clever Care Health Plan</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, SQL Server, MySQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda7cca7efaa2b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d94fa597ec855f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07441f138a32e7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806a54fa3613e0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a26778131d9f5f29</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ae74fce61007b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Shift Paradigm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f514d241530503</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2569732a012bd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Level III Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blue Margin</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e2ef8c80f8d239</t>
+          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a998218acbd3b8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Apache Spark Core Java-4</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057ed5d0ef018587</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer (Python / React)</t>
+          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Docker, Kubernetes, AKS, pytest, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
+          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1efae92e327259</t>
+          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Flink</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Fresh Consulting</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
+          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ca4dcc14f3e9e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Flink</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>FIVE STAR CREDIT UNION</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Dothan, AL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9182984ede5a4a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fresh Consulting</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e9638f73d9cb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data System Engineer DevOps</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26778131d9f5f29</t>
+          <t>https://www.indeed.com/viewjob?jk=9c21057690fd9550</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Full Stack .NET Developer (AI Augmented Engineering)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Affinity Empowering Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,497 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Shift Paradigm</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Level III Data Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Blue Margin</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Fort Collins, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Mutual of Enumclaw Insurance</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Enumclaw, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d64c7ce538beb2b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java-4</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Sysco</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Fresh Consulting</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ca4dcc14f3e9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>FIVE STAR CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Dothan, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9182984ede5a4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Fresh Consulting</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e9638f73d9cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Data System Engineer DevOps</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c21057690fd9550</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Full Stack .NET Developer (AI Augmented Engineering)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Affinity Empowering Inc.</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=887663a85634d317</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1c0a592c7badc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Scala, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15033510034f9278</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-29.xlsx
+++ b/results/job_matches_2026-08-29.xlsx
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
+          <t>Data architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0efe6a35cb61a5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Data Operations Engineer</t>
+          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
+          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Machine Learning &amp; Data Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe070deedac1b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineering Summer/Fall Co-Op (June - Dec '27)</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8446a0ee2fc12124</t>
+          <t>https://www.indeed.com/viewjob?jk=efe070deedac1b9a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)-3</t>
+          <t>Data Engineering Summer/Fall Co-Op (June - Dec '27)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8446a0ee2fc12124</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer - SMA Solutions</t>
+          <t>BI / Data Architect (Remote)-3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d538b0abcf938eb</t>
+          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>UNIX MIDDLEWARE ENGINEER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,54 +1336,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
+          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (B2B)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
+          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Finance</t>
+          <t>Senior Data Engineer-3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marlboro, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38276618e771db29</t>
+          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior CE Data Engineer</t>
+          <t>AI Data &amp; Database Engineer – Modernization &amp; AI Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8231054ab092224b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Data Engineer (B2B)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
+          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Valley Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
+          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Experience Services</t>
+          <t>Senior CE Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
+          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
+          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Valley Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
+          <t>Senior Software Engineer - Vehicle Experience Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
+          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
+          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
+          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
+          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
+          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
+          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
+          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
+          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
+          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
+          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
+          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
+          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
+          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
+          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
+          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
+          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
+          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
+          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
+          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
+          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
+          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
+          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
+          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
+          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
+          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
+          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
+          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
+          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Support</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Insurance Institute for Business and Home Safety</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richburg, SC, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, NoSQL, Data Modeling, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
+          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data, Analytics &amp; Cloud Engineering Consultant</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kenway Consulting</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1164a9e1e0387fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineering Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>ProMach</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bedminster, NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer, AI Support</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Insurance Institute for Business and Home Safety</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richburg, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Spark, Scala, NoSQL, Data Modeling, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
+          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
+          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Bedminster, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clearlink</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>New College Grad - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Clearlink</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfb93ed65fbd759</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Products</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Focus on the Family</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer Analyst</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Data Up Consulting</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
+          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Focus on the Family</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, PostgreSQL, ELT, Power BI, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce1cb75163081c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer Snowflake/Agentic AI</t>
+          <t>Python Developer Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Valtech Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebf36281f9e5d65</t>
+          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Python Developer Engineer II</t>
+          <t>Python Developer Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Python Developer Engineer</t>
+          <t>Data Engineer Analyst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data Up Consulting</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54be710cc09718e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>SDET Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c8a5b9754f3dec</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1efae92e327259</t>
+          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Flink</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
+          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Level III Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Blue Margin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Shift Paradigm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shift Paradigm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Level III Data Engineer</t>
+          <t>Apache Spark Core Java-4</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Blue Margin</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Automation Developer</t>
+          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java-4</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
+          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
+          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">

--- a/results/job_matches_2026-08-29.xlsx
+++ b/results/job_matches_2026-08-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>COREHIRE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc487e12b46c0c21</t>
+          <t>https://www.indeed.com/viewjob?jk=aef7e5280c3704dc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COREHIRE</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, clustering keys, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef7e5280c3704dc</t>
+          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, clustering keys, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
+          <t>https://www.indeed.com/viewjob?jk=1242d1109025ac15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1242d1109025ac15</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ae449ae79ca824</t>
         </is>
       </c>
     </row>
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ae449ae79ca824</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4cce7133b6d257</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4cce7133b6d257</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0efe6a35cb61a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data architect</t>
+          <t>Machine Learning &amp; Data Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0efe6a35cb61a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
+          <t>BI / Data Architect (Remote)-3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
+          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Data Operations Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Ziff Davis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
+          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
+          <t>Jr DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Koniag Government Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe070deedac1b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f140f3b3c4a71d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineering Summer/Fall Co-Op (June - Dec '27)</t>
+          <t>Senior Salesforce Subject Matter Expert (SME) - DoD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Vissat Solutions, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8446a0ee2fc12124</t>
+          <t>https://www.indeed.com/viewjob?jk=20324e69621e6432</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)-3</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=68b9213bf9a10955</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ziff Davis</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7eb57f3ad62c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a530d898f0f57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a302f6fb7238092</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jr DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koniag Government Services</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f140f3b3c4a71d9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd63cf544b64f9bc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Salesforce Subject Matter Expert (SME) - DoD</t>
+          <t>UNIX MIDDLEWARE ENGINEER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vissat Solutions, Inc</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20324e69621e6432</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect – Contract Opportunity</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IT LINK, LLC</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Downey, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847eafed624da6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b9213bf9a10955</t>
+          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7eb57f3ad62c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd63cf544b64f9bc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Senior Data Engineer-3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a302f6fb7238092</t>
+          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UNIX MIDDLEWARE ENGINEER</t>
+          <t>Senior Data Engineer (B2B)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
+          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
+          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Senior CE Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
+          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
+          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-3</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Valley Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Data &amp; Database Engineer – Modernization &amp; AI Infrastructure</t>
+          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8231054ab092224b</t>
+          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (B2B)</t>
+          <t>Senior Software Engineer - Vehicle Experience Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
+          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
+          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
+          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior CE Data Engineer</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ProMach</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Valley Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
+          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Experience Services</t>
+          <t>Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bedminster, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
+          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
+          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
+          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
+          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
+          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
+          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
+          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
+          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
+          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
+          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
+          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
+          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
+          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
+          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
+          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
+          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
+          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
+          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
+          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
+          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
+          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
+          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
+          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
+          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
+          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
+          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>Clearlink</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Support</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Insurance Institute for Business and Home Safety</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Richburg, SC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, NoSQL, Data Modeling, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
+          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
+          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineering Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bedminster, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,147 +3706,147 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
+          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Focus on the Family</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
+          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer Analyst</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Data Up Consulting</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
+          <t>Python Developer Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Clearlink</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
+          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>API Platform Owner</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
+          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Azure Solutions Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,59 +3961,59 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf200ceba06f2e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Associate Software Engineer--SAP</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0bad4738b1c25e8b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Products</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Focus on the Family</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
+          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Python Developer Engineer II</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Python Developer Engineer</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer Analyst</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Data Up Consulting</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
+          <t>https://www.indeed.com/viewjob?jk=a26778131d9f5f29</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Azure Solutions Architect</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf200ceba06f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer--SAP</t>
+          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Shift Paradigm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bad4738b1c25e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Full-Stack Software Engineer (Python / React)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Department Of Public Health</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, SQL Server, ETL, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Docker, Kubernetes, AKS, pytest, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,59 +4311,59 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576601d5caea8556</t>
+          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SDET Engineer</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c8a5b9754f3dec</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer (Python / React)</t>
+          <t>Apache Spark Core Java-4</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Docker, Kubernetes, AKS, pytest, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Flink</t>
+          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Flink</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
+          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Level III Data Engineer</t>
+          <t>Associate, Full Stack Engineer - SMA Solutions</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Blue Margin</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
+          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Fresh Consulting</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26778131d9f5f29</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ca4dcc14f3e9e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shift Paradigm</t>
+          <t>FIVE STAR CREDIT UNION</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dothan, AL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9182984ede5a4a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fresh Consulting</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e9638f73d9cb</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Automation Developer</t>
+          <t>Data System Engineer DevOps</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9c21057690fd9550</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java-4</t>
+          <t>Full Stack .NET Developer (AI Augmented Engineering)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Affinity Empowering Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,330 +4686,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Sysco</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Cloudera</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Fresh Consulting</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ca4dcc14f3e9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>FIVE STAR CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Dothan, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9182984ede5a4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Fresh Consulting</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e9638f73d9cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data System Engineer DevOps</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c21057690fd9550</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Full Stack .NET Developer (AI Augmented Engineering)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Affinity Empowering Inc.</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=887663a85634d317</t>
         </is>

--- a/results/job_matches_2026-08-29.xlsx
+++ b/results/job_matches_2026-08-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, clustering keys, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
+          <t>https://www.indeed.com/viewjob?jk=1242d1109025ac15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1242d1109025ac15</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ae449ae79ca824</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ae449ae79ca824</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4cce7133b6d257</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4cce7133b6d257</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0efe6a35cb61a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data architect</t>
+          <t>Machine Learning &amp; Data Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0efe6a35cb61a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Data Operations Engineer</t>
+          <t>BI / Data Architect (Remote)-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fdfa93f14c8a44</t>
+          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)-3</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Department of Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c68908d35bb4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c6ea2c982d3ce1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Jr DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ziff Davis</t>
+          <t>Koniag Government Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9f140f3b3c4a71d9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jr DevSecOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Koniag Government Services</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f140f3b3c4a71d9</t>
+          <t>https://www.indeed.com/viewjob?jk=68b9213bf9a10955</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Salesforce Subject Matter Expert (SME) - DoD</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vissat Solutions, Inc</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20324e69621e6432</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7eb57f3ad62c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b9213bf9a10955</t>
+          <t>https://www.indeed.com/viewjob?jk=1a302f6fb7238092</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>UNIX MIDDLEWARE ENGINEER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7eb57f3ad62c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a302f6fb7238092</t>
+          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd63cf544b64f9bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UNIX MIDDLEWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Oracle, SQL Server, ELT, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1fa99b1f49f8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,54 +1126,54 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
+          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer-3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
+          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (B2B)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbd28c2635208f</t>
+          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-3</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21e350cb2bcd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (B2B)</t>
+          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012335a0deb13e71</t>
+          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior CE Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d49a416f365a74</t>
+          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5210146e36332129</t>
+          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
+          <t>Senior Software Engineer - Vehicle Experience Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, NoSQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
+          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior CE Data Engineer</t>
+          <t>Senior Software Engineer, Investigations</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions, Terraform, pytest</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41356caeb13146a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964924f2a9a1eade</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Valley Health</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd0e7a1c9fb738d</t>
+          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Product Software Engineer II (Java/Full Stack/DevOps)</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ac0abbd64d17ed</t>
+          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Experience Services</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071fb9f341e2920c</t>
+          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
+          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2403720f77423b20</t>
+          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Investigations</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe669d1dbb76a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineering Consultant</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bedminster, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9499a84ad51357</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118609507e8326be</t>
+          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d16fcb521147d</t>
+          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f1c5e804db201c</t>
+          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225794c338d9c2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8206e033ec06c44</t>
+          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd43c72ff36db956</t>
+          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8686ee0acba4a5b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f5b6745c48702</t>
+          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e06cd90437922</t>
+          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a4f4dedb5fabe</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6693247096242514</t>
+          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808c5b23fc5eea37</t>
+          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e020bee90fd8ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d470ebbdadd6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1098b2a8732e4c94</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ac0044b561b7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4975bf08906f35bf</t>
+          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2311cfd8a6673d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b673bca486c4f22</t>
+          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6249fbe03c1348</t>
+          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68667881b72c8d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=290665b00f198eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf457c1255e3270</t>
+          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932afc1f16024fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc3b888f2ead381</t>
+          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e96cfac0656a505</t>
+          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033cddd4e55fbb32</t>
+          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0375e038f99523</t>
+          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a4edfdbeadfbe9</t>
+          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c284670db96858</t>
+          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c218c8142c65b02</t>
+          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8e2b98942a256a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435ccfa1a5ca52e0</t>
+          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66befbad411c42a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20492417b5312f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ababc96a1a969e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7540b91e1071e70</t>
+          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bedminster, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf433bc369e3f502</t>
+          <t>https://www.indeed.com/viewjob?jk=677cf280c966b0a4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Department Of Consumer Affairs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba5eba4d5412cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d29d7f0da02cd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9187eca27dea327</t>
+          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95238bc89a8e2067</t>
+          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52477e1e5bf4f0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6c02095880a60a</t>
+          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Clearlink</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da0e246efe5d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00ed81b90f4ce8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,172 +3436,172 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5cf93c087ee2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Focus on the Family</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
+          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Python Developer Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
+          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Python Developer Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Solution Architect - (Data &amp; Analytics / Cloud/ AI)</t>
+          <t>API Platform Owner</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876e98687d53ec6b</t>
+          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Solutions Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Clearlink</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4fced2d02b57e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf200ceba06f2e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Associate Software Engineer--SAP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0bad4738b1c25e8b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Data Engineer - Flink</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1690d88de11d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,137 +3751,137 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
+          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Products</t>
+          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Focus on the Family</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Time Travel, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer Analyst</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Data Up Consulting</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7ea03862f82774</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Python Developer Engineer II</t>
+          <t>Apache Spark Core Java-4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d510f452b94b43a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Developer Engineer</t>
+          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,137 +3891,137 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbeb44abc1603cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>API Platform Owner</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Azure Solutions Architect</t>
+          <t>Associate, Full Stack Engineer - SMA Solutions</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf200ceba06f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer--SAP</t>
+          <t>Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Fresh Consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bad4738b1c25e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ca4dcc14f3e9e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>FIVE STAR CREDIT UNION</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dothan, AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9182984ede5a4a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Flink</t>
+          <t>Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Fresh Consulting</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
+          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,637 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1573934d9ec37de6</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer - Flink</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Reading, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, CI/CD, Git, CloudWatch, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c68bbe7fc18ba81</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineering III</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da232191f01ac3ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a26778131d9f5f29</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, dbt, CI/CD, Terraform, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Shift Paradigm</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Full-Stack Software Engineer (Python / React)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>3Pillar Global</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Docker, Kubernetes, AKS, pytest, Airflow</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Automation Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32ec10e69dafd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java-4</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0696e0e63e0338</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Principle Software Architect, Warehouse Technology - GSC -US</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Sysco</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a6b78113f7dbbce</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69b2499e130c3cf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Cloudera</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Databricks, Dataflow, Spark, Scala, Kafka, DataOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Associate, Full Stack Engineer - SMA Solutions</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, SQL Server, PostgreSQL, DynamoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85433a570efd3e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Fresh Consulting</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ca4dcc14f3e9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>FIVE STAR CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Dothan, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9182984ede5a4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Fresh Consulting</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MySQL, MongoDB, NoSQL, CI/CD, Maven, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5919e9638f73d9cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data System Engineer DevOps</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c21057690fd9550</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Full Stack .NET Developer (AI Augmented Engineering)</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Affinity Empowering Inc.</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=887663a85634d317</t>
         </is>
       </c>
     </row>
